--- a/data/trans_bre/P34A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,74</t>
+          <t>-1,97; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 14,72</t>
+          <t>6,67; 14,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 13,97</t>
+          <t>4,5; 13,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 14,5</t>
+          <t>4,6; 14,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 14,11</t>
+          <t>-3,69; 14,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,35; 63,92</t>
+          <t>23,17; 61,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 31,4</t>
+          <t>9,07; 31,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 30,85</t>
+          <t>8,61; 30,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,51</t>
+          <t>-0,29; 6,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,12</t>
+          <t>4,41; 10,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,72</t>
+          <t>4,74; 10,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 14,2</t>
+          <t>-3,15; 14,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 17,04</t>
+          <t>-0,67; 16,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 47,15</t>
+          <t>17,48; 47,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,89; 35,75</t>
+          <t>14,06; 36,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 62,34</t>
+          <t>-9,29; 67,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 18,08</t>
+          <t>5,7; 17,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 9,76</t>
+          <t>-1,05; 9,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 10,99</t>
+          <t>0,05; 11,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 7,11</t>
+          <t>-2,34; 7,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,8; 76,07</t>
+          <t>18,8; 72,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 87,43</t>
+          <t>-7,76; 79,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 53,97</t>
+          <t>-0,07; 56,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 34,41</t>
+          <t>-8,41; 34,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,49</t>
+          <t>2,65; 7,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,66</t>
+          <t>6,47; 10,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,08</t>
+          <t>6,18; 11,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,48</t>
+          <t>1,55; 13,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,72</t>
+          <t>6,23; 18,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,29; 49,85</t>
+          <t>27,55; 50,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 33,58</t>
+          <t>17,56; 34,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 52,35</t>
+          <t>5,83; 53,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P34A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>8,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,53</t>
+          <t>-1,42; 6,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 14,57</t>
+          <t>6,51; 14,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 13,95</t>
+          <t>4,8; 14,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 14,45</t>
+          <t>3,73; 13,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 14,03</t>
+          <t>-2,55; 14,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,17; 61,21</t>
+          <t>23,07; 60,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 31,84</t>
+          <t>9,46; 32,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 30,68</t>
+          <t>6,42; 27,99</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 6,48</t>
+          <t>-0,76; 6,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,39</t>
+          <t>4,19; 10,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 10,98</t>
+          <t>4,67; 10,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 14,53</t>
+          <t>3,19; 9,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 16,86</t>
+          <t>-1,65; 16,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 47,79</t>
+          <t>16,69; 47,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 36,48</t>
+          <t>14,04; 36,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 67,32</t>
+          <t>9,39; 30,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 17,47</t>
+          <t>6,09; 18,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,2</t>
+          <t>-0,71; 9,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 11,45</t>
+          <t>0,02; 10,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,23</t>
+          <t>-1,11; 7,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 72,9</t>
+          <t>20,05; 75,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 79,49</t>
+          <t>-6,12; 85,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 56,81</t>
+          <t>0,01; 52,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 34,16</t>
+          <t>-4,76; 36,61</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,45</t>
+          <t>2,44; 7,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,89</t>
+          <t>6,1; 10,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,22</t>
+          <t>6,54; 11,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,38</t>
+          <t>4,9; 9,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,6</t>
+          <t>5,71; 18,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,55; 50,85</t>
+          <t>26,16; 49,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 34,36</t>
+          <t>18,63; 34,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 53,87</t>
+          <t>14,12; 30,42</t>
         </is>
       </c>
     </row>
